--- a/artfynd/A 16310-2022 artfynd.xlsx
+++ b/artfynd/A 16310-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,250 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125326141</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hohult, N om Ödestugu, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>458110</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6388794</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ödestugu</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Martin Oomen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Martin Oomen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125326156</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hohult, N om Ödestugu, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>458110</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6388794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ödestugu</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Oomen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Oomen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16310-2022 artfynd.xlsx
+++ b/artfynd/A 16310-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125326141</v>
+        <v>125326156</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +839,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125326156</v>
+        <v>125326141</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,11 +963,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 16310-2022 artfynd.xlsx
+++ b/artfynd/A 16310-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125326156</v>
+        <v>125326141</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,11 +839,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125326141</v>
+        <v>125326156</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,7 +959,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 16310-2022 artfynd.xlsx
+++ b/artfynd/A 16310-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125326141</v>
+        <v>125326156</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +839,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125326156</v>
+        <v>125326141</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,11 +963,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 16310-2022 artfynd.xlsx
+++ b/artfynd/A 16310-2022 artfynd.xlsx
@@ -799,32 +799,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125326156</v>
+        <v>125326141</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,11 +834,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,32 +914,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125326141</v>
+        <v>125326156</v>
       </c>
       <c r="B4" t="n">
-        <v>57573</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,7 +949,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
